--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>88960170</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368865.5036287174</v>
+        <v>368866</v>
       </c>
       <c r="R2" t="n">
-        <v>7052297.651272304</v>
+        <v>7052298</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2020-11-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-11-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,8 +775,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88960170</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88960170</v>
+        <v>135725209</v>
       </c>
       <c r="B2" t="n">
-        <v>89292</v>
+        <v>83417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hitervallen N, Jmt</t>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368866</v>
+        <v>368399</v>
       </c>
       <c r="R2" t="n">
-        <v>7052298</v>
+        <v>7052046</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-11-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-11-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,28 +761,2729 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall, Ingela Källén</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135725209</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135725195</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78458</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>314</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>368865</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7051738</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725195</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135725184</v>
+      </c>
+      <c r="B4" t="n">
+        <v>83416</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>492</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>368784</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7051905</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal grannaturskog vid Björkbevuxen myr och bäck</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725184</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135725191</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99293</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>368781</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7051895</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Björk-och gräsbevuxen myr vid bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725191</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135725198</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79519</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>283</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>368401</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7052210</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog vid bäckmiljö och myr</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725198</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135725204</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83417</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>308</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>368475</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7052158</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog i bäckravin</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725204</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135725205</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78797</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Liten sotlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Acolium karelicum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>369246</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7052603</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Lövrik och gles grannaturskog vid bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725205</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>88960170</v>
+      </c>
+      <c r="B9" t="n">
+        <v>89292</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>510</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hitervallen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>368866</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7052298</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-11-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-11-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/88960170</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135725183</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79597</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>368835</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7052225</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gransumpskog intill bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725183</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135725185</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79597</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>369466</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7053016</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Örtfattig grannaturskog vid myrkant</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725185</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135725197</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79597</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>368424</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7052195</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog i bäckravin</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725197</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135725199</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79597</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>368965</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7053197</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog vid sluttande myr</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725199</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135725187</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80554</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>368930</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7052560</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Frodig, lövbevuxen slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725187</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135725200</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80554</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>368813</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7052983</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Frodig, lövbevuxen slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725200</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135725201</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96494</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>369443</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7052902</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Lövrik och gles grannaturskog med lågörter</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725201</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135725207</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92268</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>368957</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7052837</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Örtrik fäbodskog med björk och gran</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725207</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135725186</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93029</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granriska</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>368441</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7052178</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog i bäckravin</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725186</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135725202</v>
+      </c>
+      <c r="B19" t="n">
+        <v>83423</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>368475</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7052158</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog i bäckravin</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725202</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135725189</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79519</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>283</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>368801</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7051301</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725189</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135725188</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79597</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>368801</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7051301</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725188</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135725194</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79597</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>368696</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7051227</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725194</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135725193</v>
+      </c>
+      <c r="B23" t="n">
+        <v>83289</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>368752</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7051177</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725193</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135725210</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79438</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>368223</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7050962</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725210</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135725211</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79438</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>368645</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7051015</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725211</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135725192</v>
+      </c>
+      <c r="B26" t="n">
+        <v>83425</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>368614</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7051204</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725192</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135725203</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78447</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>368629</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7051053</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725203</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88960170</v>
+        <v>135725209</v>
       </c>
       <c r="B2" t="n">
-        <v>89292</v>
+        <v>83420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hitervallen N, Jmt</t>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368866</v>
+        <v>368399</v>
       </c>
       <c r="R2" t="n">
-        <v>7052298</v>
+        <v>7052046</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-11-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-11-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,28 +761,2621 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johan Råghall, Ingela Källén</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135725209</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135725195</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78461</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>314</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vitskaftad svartspik</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis viridialba</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Kremp.) A.F.W.Schmidt</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>368865</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7051738</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725195</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135725191</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>368781</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7051895</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Björk-och gräsbevuxen myr vid bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725191</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135725198</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79522</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>283</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>368401</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7052210</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog vid bäckmiljö och myr</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725198</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135725204</v>
+      </c>
+      <c r="B6" t="n">
+        <v>83420</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>308</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>368475</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7052158</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog i bäckravin</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725204</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135725205</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78800</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Liten sotlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Acolium karelicum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>369246</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7052603</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Lövrik och gles grannaturskog vid bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725205</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>88960170</v>
+      </c>
+      <c r="B8" t="n">
+        <v>89292</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>510</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hitervallen N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>368866</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7052298</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-11-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-11-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Ingela Källén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/88960170</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135725183</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79600</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>368835</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7052225</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Gransumpskog intill bäckmiljö</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725183</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135725185</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79600</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>369466</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7053016</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Örtfattig grannaturskog vid myrkant</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725185</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135725197</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79600</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>368424</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7052195</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog i bäckravin</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725197</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135725199</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79600</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>368965</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7053197</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gles och lövrik grannaturskog vid sluttande myr</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725199</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135725187</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80557</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>368930</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7052560</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Frodig, lövbevuxen slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725187</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135725200</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80557</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>368813</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7052983</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Frodig, lövbevuxen slåtteräng</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725200</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135725201</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96499</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>369443</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7052902</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Lövrik och gles grannaturskog med lågörter</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725201</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135725207</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92273</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>368957</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7052837</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Örtrik fäbodskog med björk och gran</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725207</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135725186</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93034</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granriska</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>368441</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7052178</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog i bäckravin</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725186</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135725202</v>
+      </c>
+      <c r="B18" t="n">
+        <v>83426</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>368475</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7052158</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Örtrik grannaturskog i bäckravin</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725202</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135725189</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79522</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>283</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>368801</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7051301</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725189</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135725188</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79600</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>368801</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7051301</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725188</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135725194</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79600</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>368696</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7051227</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725194</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135725193</v>
+      </c>
+      <c r="B22" t="n">
+        <v>83292</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>368752</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7051177</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725193</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135725210</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>368223</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7050962</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Löv-och örtrik gransumpskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725210</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135725211</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>368645</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7051015</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725211</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135725192</v>
+      </c>
+      <c r="B25" t="n">
+        <v>83428</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>368614</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7051204</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725192</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135725203</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78450</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Saxvallrun-Hitervallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>368629</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7051053</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Luckig och lövrik, örtfattig grannaturskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135725203</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135725191</v>
       </c>
       <c r="B4" t="n">
-        <v>99298</v>
+        <v>99300</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135725201</v>
       </c>
       <c r="B15" t="n">
-        <v>96499</v>
+        <v>96501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135725207</v>
       </c>
       <c r="B16" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>135725186</v>
       </c>
       <c r="B17" t="n">
-        <v>93034</v>
+        <v>93036</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135725209</v>
       </c>
       <c r="B2" t="n">
-        <v>83420</v>
+        <v>83422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135725195</v>
       </c>
       <c r="B3" t="n">
-        <v>78461</v>
+        <v>78463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135725191</v>
       </c>
       <c r="B4" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135725198</v>
       </c>
       <c r="B5" t="n">
-        <v>79522</v>
+        <v>79524</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135725204</v>
       </c>
       <c r="B6" t="n">
-        <v>83420</v>
+        <v>83422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135725205</v>
       </c>
       <c r="B7" t="n">
-        <v>78800</v>
+        <v>78802</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>135725183</v>
       </c>
       <c r="B9" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>135725185</v>
       </c>
       <c r="B10" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>135725197</v>
       </c>
       <c r="B11" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>135725199</v>
       </c>
       <c r="B12" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>135725187</v>
       </c>
       <c r="B13" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>135725200</v>
       </c>
       <c r="B14" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135725201</v>
       </c>
       <c r="B15" t="n">
-        <v>96501</v>
+        <v>96518</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135725207</v>
       </c>
       <c r="B16" t="n">
-        <v>92275</v>
+        <v>92289</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>135725186</v>
       </c>
       <c r="B17" t="n">
-        <v>93036</v>
+        <v>93051</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>135725202</v>
       </c>
       <c r="B18" t="n">
-        <v>83426</v>
+        <v>83428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>135725189</v>
       </c>
       <c r="B19" t="n">
-        <v>79522</v>
+        <v>79524</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135725188</v>
       </c>
       <c r="B20" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>135725194</v>
       </c>
       <c r="B21" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135725193</v>
       </c>
       <c r="B22" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>135725210</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135725211</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135725192</v>
       </c>
       <c r="B25" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135725203</v>
       </c>
       <c r="B26" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135725209</v>
       </c>
       <c r="B2" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135725195</v>
       </c>
       <c r="B3" t="n">
-        <v>78463</v>
+        <v>78464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135725191</v>
       </c>
       <c r="B4" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135725198</v>
       </c>
       <c r="B5" t="n">
-        <v>79524</v>
+        <v>79525</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135725204</v>
       </c>
       <c r="B6" t="n">
-        <v>83422</v>
+        <v>83423</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135725205</v>
       </c>
       <c r="B7" t="n">
-        <v>78802</v>
+        <v>78803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>135725183</v>
       </c>
       <c r="B9" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>135725185</v>
       </c>
       <c r="B10" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>135725197</v>
       </c>
       <c r="B11" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>135725199</v>
       </c>
       <c r="B12" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>135725187</v>
       </c>
       <c r="B13" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>135725200</v>
       </c>
       <c r="B14" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135725201</v>
       </c>
       <c r="B15" t="n">
-        <v>96518</v>
+        <v>96519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135725207</v>
       </c>
       <c r="B16" t="n">
-        <v>92289</v>
+        <v>92290</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>135725186</v>
       </c>
       <c r="B17" t="n">
-        <v>93051</v>
+        <v>93052</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>135725202</v>
       </c>
       <c r="B18" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>135725189</v>
       </c>
       <c r="B19" t="n">
-        <v>79524</v>
+        <v>79525</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135725188</v>
       </c>
       <c r="B20" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>135725194</v>
       </c>
       <c r="B21" t="n">
-        <v>79602</v>
+        <v>79603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135725193</v>
       </c>
       <c r="B22" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>135725210</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135725211</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135725192</v>
       </c>
       <c r="B25" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135725203</v>
       </c>
       <c r="B26" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>135725191</v>
       </c>
       <c r="B4" t="n">
-        <v>99318</v>
+        <v>99319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135725201</v>
       </c>
       <c r="B15" t="n">
-        <v>96519</v>
+        <v>96520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135725207</v>
       </c>
       <c r="B16" t="n">
-        <v>92290</v>
+        <v>92291</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>135725186</v>
       </c>
       <c r="B17" t="n">
-        <v>93052</v>
+        <v>93053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135725209</v>
       </c>
       <c r="B2" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135725195</v>
       </c>
       <c r="B3" t="n">
-        <v>78464</v>
+        <v>78465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135725191</v>
       </c>
       <c r="B4" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135725198</v>
       </c>
       <c r="B5" t="n">
-        <v>79525</v>
+        <v>79526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135725204</v>
       </c>
       <c r="B6" t="n">
-        <v>83423</v>
+        <v>83424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135725205</v>
       </c>
       <c r="B7" t="n">
-        <v>78803</v>
+        <v>78804</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>135725183</v>
       </c>
       <c r="B9" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>135725185</v>
       </c>
       <c r="B10" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>135725197</v>
       </c>
       <c r="B11" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>135725199</v>
       </c>
       <c r="B12" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>135725187</v>
       </c>
       <c r="B13" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>135725200</v>
       </c>
       <c r="B14" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135725201</v>
       </c>
       <c r="B15" t="n">
-        <v>96520</v>
+        <v>96521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135725207</v>
       </c>
       <c r="B16" t="n">
-        <v>92291</v>
+        <v>92292</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>135725186</v>
       </c>
       <c r="B17" t="n">
-        <v>93053</v>
+        <v>93054</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>135725202</v>
       </c>
       <c r="B18" t="n">
-        <v>83429</v>
+        <v>83430</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>135725189</v>
       </c>
       <c r="B19" t="n">
-        <v>79525</v>
+        <v>79526</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135725188</v>
       </c>
       <c r="B20" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>135725194</v>
       </c>
       <c r="B21" t="n">
-        <v>79603</v>
+        <v>79604</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135725193</v>
       </c>
       <c r="B22" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>135725210</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135725211</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135725192</v>
       </c>
       <c r="B25" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135725203</v>
       </c>
       <c r="B26" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135725209</v>
       </c>
       <c r="B2" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135725195</v>
       </c>
       <c r="B3" t="n">
-        <v>78465</v>
+        <v>78469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135725191</v>
       </c>
       <c r="B4" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135725198</v>
       </c>
       <c r="B5" t="n">
-        <v>79526</v>
+        <v>79530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135725204</v>
       </c>
       <c r="B6" t="n">
-        <v>83424</v>
+        <v>83428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135725205</v>
       </c>
       <c r="B7" t="n">
-        <v>78804</v>
+        <v>78808</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>135725183</v>
       </c>
       <c r="B9" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>135725185</v>
       </c>
       <c r="B10" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>135725197</v>
       </c>
       <c r="B11" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>135725199</v>
       </c>
       <c r="B12" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>135725187</v>
       </c>
       <c r="B13" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>135725200</v>
       </c>
       <c r="B14" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135725201</v>
       </c>
       <c r="B15" t="n">
-        <v>96521</v>
+        <v>96527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135725207</v>
       </c>
       <c r="B16" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>135725186</v>
       </c>
       <c r="B17" t="n">
-        <v>93054</v>
+        <v>93060</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>135725202</v>
       </c>
       <c r="B18" t="n">
-        <v>83430</v>
+        <v>83434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>135725189</v>
       </c>
       <c r="B19" t="n">
-        <v>79526</v>
+        <v>79530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135725188</v>
       </c>
       <c r="B20" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>135725194</v>
       </c>
       <c r="B21" t="n">
-        <v>79604</v>
+        <v>79608</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135725193</v>
       </c>
       <c r="B22" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>135725210</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135725211</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135725192</v>
       </c>
       <c r="B25" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135725203</v>
       </c>
       <c r="B26" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135725209</v>
       </c>
       <c r="B2" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135725195</v>
       </c>
       <c r="B3" t="n">
-        <v>78469</v>
+        <v>78470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135725191</v>
       </c>
       <c r="B4" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135725198</v>
       </c>
       <c r="B5" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135725204</v>
       </c>
       <c r="B6" t="n">
-        <v>83428</v>
+        <v>83429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135725205</v>
       </c>
       <c r="B7" t="n">
-        <v>78808</v>
+        <v>78809</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>135725183</v>
       </c>
       <c r="B9" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>135725185</v>
       </c>
       <c r="B10" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>135725197</v>
       </c>
       <c r="B11" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>135725199</v>
       </c>
       <c r="B12" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>135725187</v>
       </c>
       <c r="B13" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>135725200</v>
       </c>
       <c r="B14" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135725201</v>
       </c>
       <c r="B15" t="n">
-        <v>96527</v>
+        <v>96528</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135725207</v>
       </c>
       <c r="B16" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>135725186</v>
       </c>
       <c r="B17" t="n">
-        <v>93060</v>
+        <v>93061</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>135725202</v>
       </c>
       <c r="B18" t="n">
-        <v>83434</v>
+        <v>83435</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>135725189</v>
       </c>
       <c r="B19" t="n">
-        <v>79530</v>
+        <v>79531</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135725188</v>
       </c>
       <c r="B20" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>135725194</v>
       </c>
       <c r="B21" t="n">
-        <v>79608</v>
+        <v>79609</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135725193</v>
       </c>
       <c r="B22" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>135725210</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135725211</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135725192</v>
       </c>
       <c r="B25" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135725203</v>
       </c>
       <c r="B26" t="n">
-        <v>78458</v>
+        <v>78459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 57493-2025 artfynd.xlsx
+++ b/artfynd/A 57493-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135725209</v>
       </c>
       <c r="B2" t="n">
-        <v>83429</v>
+        <v>83433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>135725195</v>
       </c>
       <c r="B3" t="n">
-        <v>78470</v>
+        <v>78474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135725191</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>135725198</v>
       </c>
       <c r="B5" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135725204</v>
       </c>
       <c r="B6" t="n">
-        <v>83429</v>
+        <v>83433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>135725205</v>
       </c>
       <c r="B7" t="n">
-        <v>78809</v>
+        <v>78813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>135725183</v>
       </c>
       <c r="B9" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>135725185</v>
       </c>
       <c r="B10" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>135725197</v>
       </c>
       <c r="B11" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>135725199</v>
       </c>
       <c r="B12" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>135725187</v>
       </c>
       <c r="B13" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>135725200</v>
       </c>
       <c r="B14" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>135725201</v>
       </c>
       <c r="B15" t="n">
-        <v>96528</v>
+        <v>96539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>135725207</v>
       </c>
       <c r="B16" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         <v>135725186</v>
       </c>
       <c r="B17" t="n">
-        <v>93061</v>
+        <v>93067</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>135725202</v>
       </c>
       <c r="B18" t="n">
-        <v>83435</v>
+        <v>83439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>135725189</v>
       </c>
       <c r="B19" t="n">
-        <v>79531</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>135725188</v>
       </c>
       <c r="B20" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>135725194</v>
       </c>
       <c r="B21" t="n">
-        <v>79609</v>
+        <v>79613</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>135725193</v>
       </c>
       <c r="B22" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>135725210</v>
       </c>
       <c r="B23" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>135725211</v>
       </c>
       <c r="B24" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135725192</v>
       </c>
       <c r="B25" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>135725203</v>
       </c>
       <c r="B26" t="n">
-        <v>78459</v>
+        <v>78463</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
